--- a/artfynd/A 13359-2024 artfynd.xlsx
+++ b/artfynd/A 13359-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116915371</v>
+        <v>116915357</v>
       </c>
       <c r="B2" t="n">
-        <v>97777</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459353</v>
+        <v>459286</v>
       </c>
       <c r="R2" t="n">
-        <v>6507155</v>
+        <v>6507148</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -765,13 +756,17 @@
           <t>2024-05-12</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>hack i basen av torraka</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,51 +789,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116915380</v>
+        <v>116915335</v>
       </c>
       <c r="B3" t="n">
-        <v>97777</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -846,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459219</v>
+        <v>459390</v>
       </c>
       <c r="R3" t="n">
-        <v>6506995</v>
+        <v>6507189</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,13 +870,17 @@
           <t>2024-05-12</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>vanlig spillning med barr</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -913,51 +903,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116915377</v>
+        <v>116915355</v>
       </c>
       <c r="B4" t="n">
-        <v>97777</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -965,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459272</v>
+        <v>459250</v>
       </c>
       <c r="R4" t="n">
-        <v>6507141</v>
+        <v>6507370</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1003,13 +984,17 @@
           <t>2024-05-12</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>spelspillning</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1032,15 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116915370</v>
+        <v>116915369</v>
       </c>
       <c r="B5" t="n">
-        <v>97777</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1047,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>145</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1084,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459215</v>
+        <v>459235</v>
       </c>
       <c r="R5" t="n">
-        <v>6507104</v>
+        <v>6507105</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1151,15 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116915372</v>
+        <v>116915370</v>
       </c>
       <c r="B6" t="n">
-        <v>97777</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1161,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1203,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459233</v>
+        <v>459215</v>
       </c>
       <c r="R6" t="n">
-        <v>6507098</v>
+        <v>6507104</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1270,15 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116915369</v>
+        <v>116915371</v>
       </c>
       <c r="B7" t="n">
-        <v>97777</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1275,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1322,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459235</v>
+        <v>459353</v>
       </c>
       <c r="R7" t="n">
-        <v>6507105</v>
+        <v>6507155</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1389,15 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116915378</v>
+        <v>116915372</v>
       </c>
       <c r="B8" t="n">
-        <v>97777</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1389,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459310</v>
+        <v>459233</v>
       </c>
       <c r="R8" t="n">
-        <v>6507167</v>
+        <v>6507098</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1511,12 +1476,7 @@
         <v>116915373</v>
       </c>
       <c r="B9" t="n">
-        <v>97777</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,15 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116915384</v>
+        <v>116915374</v>
       </c>
       <c r="B10" t="n">
-        <v>97777</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1617,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1679,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459250</v>
+        <v>459214</v>
       </c>
       <c r="R10" t="n">
-        <v>6507035</v>
+        <v>6507095</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1746,15 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116915383</v>
+        <v>116915375</v>
       </c>
       <c r="B11" t="n">
-        <v>97777</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1731,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1798,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459291</v>
+        <v>459390</v>
       </c>
       <c r="R11" t="n">
-        <v>6507033</v>
+        <v>6507192</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1865,47 +1815,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116915335</v>
+        <v>116915377</v>
       </c>
       <c r="B12" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1913,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459390</v>
+        <v>459272</v>
       </c>
       <c r="R12" t="n">
-        <v>6507189</v>
+        <v>6507141</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1951,17 +1900,13 @@
           <t>2024-05-12</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>vanlig spillning med barr</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1984,42 +1929,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116915394</v>
+        <v>116915378</v>
       </c>
       <c r="B13" t="n">
-        <v>104867</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2036,10 +1976,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459256</v>
+        <v>459310</v>
       </c>
       <c r="R13" t="n">
-        <v>6507355</v>
+        <v>6507167</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2103,15 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>116915374</v>
+        <v>116915379</v>
       </c>
       <c r="B14" t="n">
-        <v>97777</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2073,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2155,10 +2090,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459214</v>
+        <v>459281</v>
       </c>
       <c r="R14" t="n">
-        <v>6507095</v>
+        <v>6507154</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2222,15 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>116915379</v>
+        <v>116915380</v>
       </c>
       <c r="B15" t="n">
-        <v>97777</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2187,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2274,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459281</v>
+        <v>459219</v>
       </c>
       <c r="R15" t="n">
-        <v>6507154</v>
+        <v>6506995</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2341,15 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>116915375</v>
+        <v>116915381</v>
       </c>
       <c r="B16" t="n">
-        <v>97777</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,7 +2301,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2393,10 +2318,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459390</v>
+        <v>459300</v>
       </c>
       <c r="R16" t="n">
-        <v>6507192</v>
+        <v>6507137</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2460,42 +2385,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>116915389</v>
+        <v>116915383</v>
       </c>
       <c r="B17" t="n">
-        <v>104867</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2512,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459332</v>
+        <v>459291</v>
       </c>
       <c r="R17" t="n">
-        <v>6506996</v>
+        <v>6507033</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2579,47 +2499,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>116915357</v>
+        <v>116915384</v>
       </c>
       <c r="B18" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2627,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459286</v>
+        <v>459250</v>
       </c>
       <c r="R18" t="n">
-        <v>6507148</v>
+        <v>6507035</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2665,17 +2584,13 @@
           <t>2024-05-12</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hack i basen av torraka</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2698,42 +2613,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>116915381</v>
+        <v>116915389</v>
       </c>
       <c r="B19" t="n">
-        <v>97777</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2750,10 +2660,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459300</v>
+        <v>459332</v>
       </c>
       <c r="R19" t="n">
-        <v>6507137</v>
+        <v>6506996</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2810,6 +2720,120 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>116915394</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Råbockamossen-Ormåsamossarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>459256</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6507355</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Rolf-Göran Carlsson, Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
         <is>
           <t>Skogsgruppen Skaraborg</t>
         </is>

--- a/artfynd/A 13359-2024 artfynd.xlsx
+++ b/artfynd/A 13359-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915357</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915335</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915355</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915369</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915370</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,6 +1386,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915371</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,6 +1505,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915372</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915373</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1698,6 +1743,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915374</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1812,6 +1862,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915375</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1926,6 +1981,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915377</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2040,6 +2100,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915378</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2154,6 +2219,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915379</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2268,6 +2338,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915380</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2382,6 +2457,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915381</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2496,6 +2576,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915383</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2610,6 +2695,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915384</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2724,6 +2814,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915389</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2838,8 +2933,34 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915394</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>